--- a/Result/profitability/1535.xlsx
+++ b/Result/profitability/1535.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>0.9625</v>
+        <v>0.95625</v>
       </c>
       <c r="N2" t="n">
-        <v>9.956250000000001</v>
+        <v>10.28</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,16 +780,16 @@
         <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>0.97375</v>
+        <v>0.9325</v>
       </c>
       <c r="N3" t="n">
-        <v>9.945</v>
+        <v>10.0825</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -798,7 +798,7 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>1.06</v>
       </c>
       <c r="M4" t="n">
-        <v>0.95625</v>
+        <v>0.9550000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>9.5525</v>
+        <v>9.75625</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.71</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.9199999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>9.42375</v>
+        <v>9.8575</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,16 +1137,16 @@
         <v>0.85</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9175</v>
+        <v>0.91125</v>
       </c>
       <c r="N6" t="n">
-        <v>9.512499999999999</v>
+        <v>10.01125</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1155,7 +1155,7 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.85</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9087499999999999</v>
+        <v>0.86625</v>
       </c>
       <c r="N7" t="n">
-        <v>10.06</v>
+        <v>9.998750000000001</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1279,7 +1279,7 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.9</v>
       </c>
       <c r="M8" t="n">
-        <v>0.87</v>
+        <v>0.8825000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>10.0325</v>
+        <v>10.03875</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>1.1</v>
       </c>
       <c r="M9" t="n">
-        <v>0.9112499999999999</v>
+        <v>0.9112500000000001</v>
       </c>
       <c r="N9" t="n">
         <v>10.135</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1535</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1984</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1752</v>
+      </c>
+      <c r="E75" t="n">
+        <v>232</v>
+      </c>
+      <c r="F75" t="n">
+        <v>11.69</v>
+      </c>
+      <c r="G75" t="n">
+        <v>91</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>4.56%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>41</v>
+      </c>
+      <c r="J75" t="n">
+        <v>132</v>
+      </c>
+      <c r="K75" t="n">
+        <v>108</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="N75" t="n">
+        <v>10.1475</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.1298701298701299</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.04999999999999893</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.004295532646048095</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.1212121212121212</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>3.469999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.4221411192214111</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
